--- a/artfynd/A 40411-2021 artfynd.xlsx
+++ b/artfynd/A 40411-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40411-2021 artfynd.xlsx
+++ b/artfynd/A 40411-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>47240</v>
+        <v>94650337</v>
       </c>
       <c r="B2" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>201075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +708,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björsbo, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571731.5610733986</v>
+        <v>571748</v>
       </c>
       <c r="R2" t="n">
-        <v>6617048.442981317</v>
+        <v>6617048</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-07-20</t>
+          <t>2021-07-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-07-20</t>
+          <t>2021-07-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,9 +781,15 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Trädgård, örtrika gräsmarker</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -793,6 +802,229 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>47240</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>571732</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6617048</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2165987</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98695</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219606</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pilblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sagittaria sagittifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571670</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6617032</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-07-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sjö</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40411-2021 artfynd.xlsx
+++ b/artfynd/A 40411-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134744101</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100815</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219851</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hässlebrodd</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Milium effusum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571660</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6616961</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40411-2021 artfynd.xlsx
+++ b/artfynd/A 40411-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94650337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47240</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2165987</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134744101</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>